--- a/data/empregos_setores_ipece.xlsx
+++ b/data/empregos_setores_ipece.xlsx
@@ -634,7 +634,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -699,10 +699,10 @@
     <xf numFmtId="37" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -718,6 +718,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
